--- a/Field-trails/2025-11-05-Pig-Slurry/DFC overview pig.xlsx
+++ b/Field-trails/2025-11-05-Pig-Slurry/DFC overview pig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\Pig-Slurry 2025-11-05\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-11-05-Pig-Slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999721EB-CC28-4CD8-9604-A76F428A2C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED3D62F-47B5-469A-A226-7E546018DD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,8 +35,27 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={1F78B895-D85C-4922-97A4-38A181EFBF3B}</author>
+  </authors>
+  <commentList>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{1F78B895-D85C-4922-97A4-38A181EFBF3B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Time of slurry application in relation to the start of the experiment
+(bks simply corrected to use the 1st measurement point)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>Notes</t>
   </si>
@@ -158,6 +177,9 @@
   <si>
     <t>RAW</t>
   </si>
+  <si>
+    <t>Δt [h]</t>
+  </si>
 </sst>
 </file>
 
@@ -166,7 +188,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +206,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -207,12 +235,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -228,6 +257,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Mikael Løvig Larsen" id="{DB2C1B22-E491-4202-AEFE-EDDF00FCCA1A}" userId="S::au705323@uni.au.dk::501b5c6e-34b9-41fc-bcf2-dc0650cde639" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -491,18 +526,28 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="I1" dT="2026-03-04T10:16:56.49" personId="{DB2C1B22-E491-4202-AEFE-EDDF00FCCA1A}" id="{1F78B895-D85C-4922-97A4-38A181EFBF3B}">
+    <text>Time of slurry application in relation to the start of the experiment
+(bks simply corrected to use the 1st measurement point)</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>45966</v>
       </c>
@@ -521,20 +566,23 @@
       <c r="G1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>26</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -551,23 +599,29 @@
         <v>132.80000000000001</v>
       </c>
       <c r="G2" s="4">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="H2">
-        <f>(F2^0.5)*$J$2</f>
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>(F2^0.5)*$L$2</f>
         <v>34.571664698131038</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>3</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -584,14 +638,21 @@
         <v>123.1</v>
       </c>
       <c r="G3" s="4">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H20" si="0">(F3^0.5)*$J$2</f>
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="H3" s="4">
+        <f>G3-$G$2</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>(F3^0.5)*$L$2</f>
         <v>33.285131815872383</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -608,14 +669,21 @@
         <v>122.6</v>
       </c>
       <c r="G4" s="4">
-        <v>0.49166666666666697</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="0"/>
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" ref="H4:H20" si="0">G4-$G$2</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>(F4^0.5)*$L$2</f>
         <v>33.217465285599381</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -632,14 +700,22 @@
         <v>122.7</v>
       </c>
       <c r="G5" s="4">
-        <v>0.50138888888888888</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
+        <v>0.50277777777777777</v>
+      </c>
+      <c r="H5" s="4">
+        <f>G5-$G$2</f>
+        <v>1.6666666666666663E-2</v>
+      </c>
+      <c r="I5" s="5">
+        <f>24/60</f>
+        <v>0.4</v>
+      </c>
+      <c r="J5">
+        <f>(F5^0.5)*$L$2</f>
         <v>33.231009614515173</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -656,14 +732,22 @@
         <v>122.7</v>
       </c>
       <c r="G6" s="4">
-        <v>0.50138888888888888</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="0"/>
+        <v>2.2222222222222199E-2</v>
+      </c>
+      <c r="I6" s="5">
+        <f>32/60</f>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="J6">
+        <f>(F6^0.5)*$L$2</f>
         <v>33.231009614515173</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>6</v>
       </c>
@@ -677,14 +761,22 @@
         <v>125.5</v>
       </c>
       <c r="G7" s="4">
-        <v>0.50138888888888899</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
+        <v>0.50277777777777777</v>
+      </c>
+      <c r="H7" s="4">
+        <f t="shared" si="0"/>
+        <v>1.6666666666666663E-2</v>
+      </c>
+      <c r="I7" s="5">
+        <f>24/60</f>
+        <v>0.4</v>
+      </c>
+      <c r="J7">
+        <f>(F7^0.5)*$L$2</f>
         <v>33.608034753612117</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -701,14 +793,22 @@
         <v>128.80000000000001</v>
       </c>
       <c r="G8" s="4">
-        <v>0.50138888888888899</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
+        <v>0.50277777777777777</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.6666666666666663E-2</v>
+      </c>
+      <c r="I8" s="5">
+        <f>24/60</f>
+        <v>0.4</v>
+      </c>
+      <c r="J8">
+        <f>(F8^0.5)*$L$2</f>
         <v>34.047026301866659</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>8</v>
       </c>
@@ -722,14 +822,22 @@
         <v>126.9</v>
       </c>
       <c r="G9" s="4">
-        <v>7.7083333333333337E-2</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
+        <v>0.57777777777777772</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" si="0"/>
+        <v>9.1666666666666619E-2</v>
+      </c>
+      <c r="I9" s="5">
+        <f>(2*60+12)/60</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J9">
+        <f>(F9^0.5)*$L$2</f>
         <v>33.79497003993346</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -746,14 +854,22 @@
         <v>126.9</v>
       </c>
       <c r="G10" s="4">
-        <v>7.7083333333333337E-2</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="0"/>
+        <v>8.5416666666666641E-2</v>
+      </c>
+      <c r="I10">
+        <f>(2*60+3)/60</f>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="J10">
+        <f>(F10^0.5)*$L$2</f>
         <v>33.79497003993346</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -770,14 +886,22 @@
         <v>129.4</v>
       </c>
       <c r="G11" s="4">
-        <v>8.4722222222222227E-2</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="H11" s="4">
+        <f t="shared" si="0"/>
+        <v>9.7916666666666707E-2</v>
+      </c>
+      <c r="I11" s="5">
+        <f>(2*60+21)/60</f>
+        <v>2.35</v>
+      </c>
+      <c r="J11">
+        <f>(F11^0.5)*$L$2</f>
         <v>34.126236241343697</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C12">
         <v>11</v>
       </c>
@@ -791,14 +915,22 @@
         <v>121.4</v>
       </c>
       <c r="G12" s="4">
-        <v>9.0277777777777776E-2</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
+        <v>0.58958333333333335</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" si="0"/>
+        <v>0.10347222222222224</v>
+      </c>
+      <c r="I12" s="5">
+        <f>(2*60+29)/60</f>
+        <v>2.4833333333333334</v>
+      </c>
+      <c r="J12">
+        <f>(F12^0.5)*$L$2</f>
         <v>33.054500450014373</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -815,14 +947,22 @@
         <v>124.3</v>
       </c>
       <c r="G13" s="4">
-        <v>9.5138888888888884E-2</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="0"/>
+        <v>0.59513888888888888</v>
+      </c>
+      <c r="H13" s="4">
+        <f t="shared" si="0"/>
+        <v>0.10902777777777778</v>
+      </c>
+      <c r="I13" s="5">
+        <f>(2*60+37)/60</f>
+        <v>2.6166666666666667</v>
+      </c>
+      <c r="J13">
+        <f>(F13^0.5)*$L$2</f>
         <v>33.446972957204963</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -839,14 +979,22 @@
         <v>125</v>
       </c>
       <c r="G14" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="0"/>
+        <v>0.11458333333333331</v>
+      </c>
+      <c r="I14">
+        <f>(2*60+45)/60</f>
+        <v>2.75</v>
+      </c>
+      <c r="J14">
+        <f>(F14^0.5)*$L$2</f>
         <v>33.541019662496851</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>14</v>
       </c>
@@ -860,14 +1008,22 @@
         <v>126.5</v>
       </c>
       <c r="G15" s="4">
-        <v>0.10555555555555556</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="0"/>
+        <v>0.60624999999999996</v>
+      </c>
+      <c r="H15" s="4">
+        <f t="shared" si="0"/>
+        <v>0.12013888888888885</v>
+      </c>
+      <c r="I15" s="5">
+        <f>(2*60+53)/60</f>
+        <v>2.8833333333333333</v>
+      </c>
+      <c r="J15">
+        <f>(F15^0.5)*$L$2</f>
         <v>33.741665637605976</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -884,14 +1040,22 @@
         <v>143.1</v>
       </c>
       <c r="G16" s="4">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="0"/>
+        <v>0.6118055555555556</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="0"/>
+        <v>0.1256944444444445</v>
+      </c>
+      <c r="I16" s="5">
+        <f>(3*60+1)/60</f>
+        <v>3.0166666666666666</v>
+      </c>
+      <c r="J16">
+        <f>(F16^0.5)*$L$2</f>
         <v>35.887323667278395</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -908,14 +1072,22 @@
         <v>143.1</v>
       </c>
       <c r="G17" s="4">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="0"/>
+        <v>0.61736111111111114</v>
+      </c>
+      <c r="H17" s="4">
+        <f t="shared" si="0"/>
+        <v>0.13125000000000003</v>
+      </c>
+      <c r="I17" s="5">
+        <f>(3*60+9)/60</f>
+        <v>3.15</v>
+      </c>
+      <c r="J17">
+        <f>(F17^0.5)*$L$2</f>
         <v>35.887323667278395</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C18">
         <v>17</v>
       </c>
@@ -929,14 +1101,22 @@
         <v>135.30000000000001</v>
       </c>
       <c r="G18" s="4">
-        <v>0.12222222222222222</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="0"/>
+        <v>0.62291666666666667</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="0"/>
+        <v>0.13680555555555557</v>
+      </c>
+      <c r="I18" s="5">
+        <f>(3*60+17)/60</f>
+        <v>3.2833333333333332</v>
+      </c>
+      <c r="J18">
+        <f>(F18^0.5)*$L$2</f>
         <v>34.895558456628834</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -953,14 +1133,22 @@
         <v>124.4</v>
       </c>
       <c r="G19" s="4">
-        <v>0.12777777777777777</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="0"/>
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="H19" s="4">
+        <f t="shared" si="0"/>
+        <v>0.1423611111111111</v>
+      </c>
+      <c r="I19" s="5">
+        <f>(3*60+25)/60</f>
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="J19">
+        <f>(F19^0.5)*$L$2</f>
         <v>33.460424384636852</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -977,14 +1165,23 @@
         <v>129.30000000000001</v>
       </c>
       <c r="G20" s="4">
-        <v>0.133333333333333</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="0"/>
+        <v>0.63402777777777775</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" si="0"/>
+        <v>0.14791666666666664</v>
+      </c>
+      <c r="I20">
+        <f>(3*60+33)/60</f>
+        <v>3.55</v>
+      </c>
+      <c r="J20">
+        <f>(F20^0.5)*$L$2</f>
         <v>34.113047357279591</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Field-trails/2025-11-05-Pig-Slurry/DFC overview pig.xlsx
+++ b/Field-trails/2025-11-05-Pig-Slurry/DFC overview pig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-11-05-Pig-Slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED3D62F-47B5-469A-A226-7E546018DD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF85691F-BE76-4693-94B8-7E2D63571FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -38,10 +38,19 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={AA1BF658-B979-4146-9A0E-C46AC07D3CE1}</author>
     <author>tc={1F78B895-D85C-4922-97A4-38A181EFBF3B}</author>
   </authors>
   <commentList>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{1F78B895-D85C-4922-97A4-38A181EFBF3B}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{AA1BF658-B979-4146-9A0E-C46AC07D3CE1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This colum follows the original plan during the experiment, but OSI and TH was switched on the actual day for logistical reasons</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{1F78B895-D85C-4922-97A4-38A181EFBF3B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -528,6 +537,9 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E1" dT="2026-03-12T08:15:27.29" personId="{DB2C1B22-E491-4202-AEFE-EDDF00FCCA1A}" id="{AA1BF658-B979-4146-9A0E-C46AC07D3CE1}">
+    <text>This colum follows the original plan during the experiment, but OSI and TH was switched on the actual day for logistical reasons</text>
+  </threadedComment>
   <threadedComment ref="I1" dT="2026-03-04T10:16:56.49" personId="{DB2C1B22-E491-4202-AEFE-EDDF00FCCA1A}" id="{1F78B895-D85C-4922-97A4-38A181EFBF3B}">
     <text>Time of slurry application in relation to the start of the experiment
 (bks simply corrected to use the 1st measurement point)</text>
@@ -608,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <f>(F2^0.5)*$L$2</f>
+        <f t="shared" ref="J2:J20" si="0">(F2^0.5)*$L$2</f>
         <v>34.571664698131038</v>
       </c>
       <c r="L2">
@@ -648,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <f>(F3^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.285131815872383</v>
       </c>
     </row>
@@ -672,14 +684,14 @@
         <v>0.4861111111111111</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" ref="H4:H20" si="0">G4-$G$2</f>
+        <f t="shared" ref="H4:H20" si="1">G4-$G$2</f>
         <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <f>(F4^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.217465285599381</v>
       </c>
     </row>
@@ -711,7 +723,7 @@
         <v>0.4</v>
       </c>
       <c r="J5">
-        <f>(F5^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.231009614515173</v>
       </c>
     </row>
@@ -735,7 +747,7 @@
         <v>0.5083333333333333</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.2222222222222199E-2</v>
       </c>
       <c r="I6" s="5">
@@ -743,7 +755,7 @@
         <v>0.53333333333333333</v>
       </c>
       <c r="J6">
-        <f>(F6^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.231009614515173</v>
       </c>
     </row>
@@ -764,7 +776,7 @@
         <v>0.50277777777777777</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.6666666666666663E-2</v>
       </c>
       <c r="I7" s="5">
@@ -772,7 +784,7 @@
         <v>0.4</v>
       </c>
       <c r="J7">
-        <f>(F7^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.608034753612117</v>
       </c>
     </row>
@@ -796,7 +808,7 @@
         <v>0.50277777777777777</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.6666666666666663E-2</v>
       </c>
       <c r="I8" s="5">
@@ -804,7 +816,7 @@
         <v>0.4</v>
       </c>
       <c r="J8">
-        <f>(F8^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>34.047026301866659</v>
       </c>
     </row>
@@ -825,7 +837,7 @@
         <v>0.57777777777777772</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.1666666666666619E-2</v>
       </c>
       <c r="I9" s="5">
@@ -833,7 +845,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J9">
-        <f>(F9^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.79497003993346</v>
       </c>
     </row>
@@ -857,7 +869,7 @@
         <v>0.57152777777777775</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.5416666666666641E-2</v>
       </c>
       <c r="I10">
@@ -865,7 +877,7 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="J10">
-        <f>(F10^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.79497003993346</v>
       </c>
     </row>
@@ -889,7 +901,7 @@
         <v>0.58402777777777781</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.7916666666666707E-2</v>
       </c>
       <c r="I11" s="5">
@@ -897,7 +909,7 @@
         <v>2.35</v>
       </c>
       <c r="J11">
-        <f>(F11^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>34.126236241343697</v>
       </c>
     </row>
@@ -918,7 +930,7 @@
         <v>0.58958333333333335</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.10347222222222224</v>
       </c>
       <c r="I12" s="5">
@@ -926,7 +938,7 @@
         <v>2.4833333333333334</v>
       </c>
       <c r="J12">
-        <f>(F12^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.054500450014373</v>
       </c>
     </row>
@@ -950,7 +962,7 @@
         <v>0.59513888888888888</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.10902777777777778</v>
       </c>
       <c r="I13" s="5">
@@ -958,7 +970,7 @@
         <v>2.6166666666666667</v>
       </c>
       <c r="J13">
-        <f>(F13^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.446972957204963</v>
       </c>
     </row>
@@ -982,7 +994,7 @@
         <v>0.60069444444444442</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11458333333333331</v>
       </c>
       <c r="I14">
@@ -990,7 +1002,7 @@
         <v>2.75</v>
       </c>
       <c r="J14">
-        <f>(F14^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.541019662496851</v>
       </c>
     </row>
@@ -1011,7 +1023,7 @@
         <v>0.60624999999999996</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.12013888888888885</v>
       </c>
       <c r="I15" s="5">
@@ -1019,7 +1031,7 @@
         <v>2.8833333333333333</v>
       </c>
       <c r="J15">
-        <f>(F15^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.741665637605976</v>
       </c>
     </row>
@@ -1043,7 +1055,7 @@
         <v>0.6118055555555556</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.1256944444444445</v>
       </c>
       <c r="I16" s="5">
@@ -1051,7 +1063,7 @@
         <v>3.0166666666666666</v>
       </c>
       <c r="J16">
-        <f>(F16^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>35.887323667278395</v>
       </c>
     </row>
@@ -1075,7 +1087,7 @@
         <v>0.61736111111111114</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.13125000000000003</v>
       </c>
       <c r="I17" s="5">
@@ -1083,7 +1095,7 @@
         <v>3.15</v>
       </c>
       <c r="J17">
-        <f>(F17^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>35.887323667278395</v>
       </c>
     </row>
@@ -1104,7 +1116,7 @@
         <v>0.62291666666666667</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.13680555555555557</v>
       </c>
       <c r="I18" s="5">
@@ -1112,7 +1124,7 @@
         <v>3.2833333333333332</v>
       </c>
       <c r="J18">
-        <f>(F18^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>34.895558456628834</v>
       </c>
     </row>
@@ -1136,7 +1148,7 @@
         <v>0.62847222222222221</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.1423611111111111</v>
       </c>
       <c r="I19" s="5">
@@ -1144,7 +1156,7 @@
         <v>3.4166666666666665</v>
       </c>
       <c r="J19">
-        <f>(F19^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>33.460424384636852</v>
       </c>
     </row>
@@ -1168,7 +1180,7 @@
         <v>0.63402777777777775</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.14791666666666664</v>
       </c>
       <c r="I20">
@@ -1176,7 +1188,7 @@
         <v>3.55</v>
       </c>
       <c r="J20">
-        <f>(F20^0.5)*$L$2</f>
+        <f t="shared" si="0"/>
         <v>34.113047357279591</v>
       </c>
     </row>

--- a/Field-trails/2025-11-05-Pig-Slurry/DFC overview pig.xlsx
+++ b/Field-trails/2025-11-05-Pig-Slurry/DFC overview pig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-11-05-Pig-Slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF85691F-BE76-4693-94B8-7E2D63571FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFAFD2F-6E46-439F-B9FA-E768F6DB269B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -197,7 +197,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,12 +215,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -244,13 +238,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -920,7 +915,7 @@
       <c r="D12">
         <v>9</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F12">

--- a/Field-trails/2025-11-05-Pig-Slurry/DFC overview pig.xlsx
+++ b/Field-trails/2025-11-05-Pig-Slurry/DFC overview pig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-11-05-Pig-Slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFAFD2F-6E46-439F-B9FA-E768F6DB269B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A4BA72-901F-465F-8851-B99514D2E69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>Notes</t>
   </si>
@@ -189,6 +189,18 @@
   <si>
     <t>Δt [h]</t>
   </si>
+  <si>
+    <t>Chamber volume</t>
+  </si>
+  <si>
+    <t>[L]</t>
+  </si>
+  <si>
+    <t>AER [1/s]</t>
+  </si>
+  <si>
+    <t>AER [1/min]</t>
+  </si>
 </sst>
 </file>
 
@@ -197,7 +209,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,6 +228,14 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -245,7 +265,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.109375" bestFit="1" customWidth="1"/>
@@ -552,9 +572,11 @@
     <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>45966</v>
       </c>
@@ -579,17 +601,23 @@
       <c r="J1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L1" t="s">
+      <c r="K1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -615,20 +643,28 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J20" si="0">(F2^0.5)*$L$2</f>
+        <f>(F2^0.5)*$N$2</f>
         <v>34.571664698131038</v>
       </c>
-      <c r="L2">
+      <c r="K2">
+        <f>J2/$N$3</f>
+        <v>0.23047776465420691</v>
+      </c>
+      <c r="L2" s="5">
+        <f>K2*60</f>
+        <v>13.828665879252414</v>
+      </c>
+      <c r="N2">
         <v>3</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -655,11 +691,28 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <f t="shared" si="0"/>
+        <f>(F3^0.5)*$N$2</f>
         <v>33.285131815872383</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <f>J3/$N$3</f>
+        <v>0.22190087877248255</v>
+      </c>
+      <c r="L3" s="5">
+        <f t="shared" ref="L3:L20" si="0">K3*60</f>
+        <v>13.314052726348953</v>
+      </c>
+      <c r="N3">
+        <v>150</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -686,11 +739,19 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
+        <f>(F4^0.5)*$N$2</f>
         <v>33.217465285599381</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <f>J4/$N$3</f>
+        <v>0.22144976857066254</v>
+      </c>
+      <c r="L4" s="5">
+        <f t="shared" si="0"/>
+        <v>13.286986114239753</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -718,11 +779,19 @@
         <v>0.4</v>
       </c>
       <c r="J5">
-        <f t="shared" si="0"/>
+        <f>(F5^0.5)*$N$2</f>
         <v>33.231009614515173</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <f>J5/$N$3</f>
+        <v>0.22154006409676782</v>
+      </c>
+      <c r="L5" s="5">
+        <f t="shared" si="0"/>
+        <v>13.292403845806069</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -750,11 +819,19 @@
         <v>0.53333333333333333</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
+        <f>(F6^0.5)*$N$2</f>
         <v>33.231009614515173</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K6">
+        <f>J6/$N$3</f>
+        <v>0.22154006409676782</v>
+      </c>
+      <c r="L6" s="5">
+        <f t="shared" si="0"/>
+        <v>13.292403845806069</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>6</v>
       </c>
@@ -779,11 +856,19 @@
         <v>0.4</v>
       </c>
       <c r="J7">
-        <f t="shared" si="0"/>
+        <f>(F7^0.5)*$N$2</f>
         <v>33.608034753612117</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K7">
+        <f>J7/$N$3</f>
+        <v>0.22405356502408078</v>
+      </c>
+      <c r="L7" s="5">
+        <f t="shared" si="0"/>
+        <v>13.443213901444846</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -811,11 +896,19 @@
         <v>0.4</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
+        <f>(F8^0.5)*$N$2</f>
         <v>34.047026301866659</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <f>J8/$N$3</f>
+        <v>0.22698017534577772</v>
+      </c>
+      <c r="L8" s="5">
+        <f t="shared" si="0"/>
+        <v>13.618810520746663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>8</v>
       </c>
@@ -840,11 +933,19 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J9">
-        <f t="shared" si="0"/>
+        <f>(F9^0.5)*$N$2</f>
         <v>33.79497003993346</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <f>J9/$N$3</f>
+        <v>0.22529980026622307</v>
+      </c>
+      <c r="L9" s="5">
+        <f t="shared" si="0"/>
+        <v>13.517988015973383</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -872,11 +973,19 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="J10">
-        <f t="shared" si="0"/>
+        <f>(F10^0.5)*$N$2</f>
         <v>33.79497003993346</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <f>J10/$N$3</f>
+        <v>0.22529980026622307</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" si="0"/>
+        <v>13.517988015973383</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -904,18 +1013,26 @@
         <v>2.35</v>
       </c>
       <c r="J11">
-        <f t="shared" si="0"/>
+        <f>(F11^0.5)*$N$2</f>
         <v>34.126236241343697</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K11">
+        <f>J11/$N$3</f>
+        <v>0.227508241608958</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="0"/>
+        <v>13.65049449653748</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12">
         <v>9</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12">
@@ -933,11 +1050,19 @@
         <v>2.4833333333333334</v>
       </c>
       <c r="J12">
-        <f t="shared" si="0"/>
+        <f>(F12^0.5)*$N$2</f>
         <v>33.054500450014373</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K12">
+        <f>J12/$N$3</f>
+        <v>0.22036333633342917</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="0"/>
+        <v>13.221800180005751</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -965,11 +1090,19 @@
         <v>2.6166666666666667</v>
       </c>
       <c r="J13">
-        <f t="shared" si="0"/>
+        <f>(F13^0.5)*$N$2</f>
         <v>33.446972957204963</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K13">
+        <f>J13/$N$3</f>
+        <v>0.22297981971469974</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="0"/>
+        <v>13.378789182881984</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -997,11 +1130,19 @@
         <v>2.75</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
+        <f>(F14^0.5)*$N$2</f>
         <v>33.541019662496851</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K14">
+        <f>J14/$N$3</f>
+        <v>0.22360679774997899</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="0"/>
+        <v>13.416407864998739</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>14</v>
       </c>
@@ -1026,11 +1167,19 @@
         <v>2.8833333333333333</v>
       </c>
       <c r="J15">
-        <f t="shared" si="0"/>
+        <f>(F15^0.5)*$N$2</f>
         <v>33.741665637605976</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K15">
+        <f>J15/$N$3</f>
+        <v>0.22494443758403984</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="0"/>
+        <v>13.49666625504239</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1058,11 +1207,19 @@
         <v>3.0166666666666666</v>
       </c>
       <c r="J16">
-        <f t="shared" si="0"/>
+        <f>(F16^0.5)*$N$2</f>
         <v>35.887323667278395</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16">
+        <f>J16/$N$3</f>
+        <v>0.23924882444852263</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="0"/>
+        <v>14.354929466911358</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1090,11 +1247,19 @@
         <v>3.15</v>
       </c>
       <c r="J17">
-        <f t="shared" si="0"/>
+        <f>(F17^0.5)*$N$2</f>
         <v>35.887323667278395</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17">
+        <f>J17/$N$3</f>
+        <v>0.23924882444852263</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="0"/>
+        <v>14.354929466911358</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C18">
         <v>17</v>
       </c>
@@ -1119,11 +1284,19 @@
         <v>3.2833333333333332</v>
       </c>
       <c r="J18">
-        <f t="shared" si="0"/>
+        <f>(F18^0.5)*$N$2</f>
         <v>34.895558456628834</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18">
+        <f>J18/$N$3</f>
+        <v>0.23263705637752555</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="0"/>
+        <v>13.958223382651532</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1151,11 +1324,19 @@
         <v>3.4166666666666665</v>
       </c>
       <c r="J19">
-        <f t="shared" si="0"/>
+        <f>(F19^0.5)*$N$2</f>
         <v>33.460424384636852</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19">
+        <f>J19/$N$3</f>
+        <v>0.22306949589757902</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="0"/>
+        <v>13.38416975385474</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1183,8 +1364,16 @@
         <v>3.55</v>
       </c>
       <c r="J20">
-        <f t="shared" si="0"/>
+        <f>(F20^0.5)*$N$2</f>
         <v>34.113047357279591</v>
+      </c>
+      <c r="K20">
+        <f>J20/$N$3</f>
+        <v>0.22742031571519727</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="0"/>
+        <v>13.645218942911836</v>
       </c>
     </row>
   </sheetData>

--- a/Field-trails/2025-11-05-Pig-Slurry/DFC overview pig.xlsx
+++ b/Field-trails/2025-11-05-Pig-Slurry/DFC overview pig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-11-05-Pig-Slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A4BA72-901F-465F-8851-B99514D2E69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FE100C-C0D3-47FB-AC63-796B15F4CCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,6 +703,7 @@
         <v>13.314052726348953</v>
       </c>
       <c r="N3">
+        <f>0.15*1000</f>
         <v>150</v>
       </c>
       <c r="O3" t="s">
